--- a/src/reports/empresas.xlsx
+++ b/src/reports/empresas.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Nombre</t>
   </si>
@@ -28,40 +28,7 @@
     <t>PBX</t>
   </si>
   <si>
-    <t>Constructora Peralta</t>
-  </si>
-  <si>
-    <t>Bajo</t>
-  </si>
-  <si>
-    <t>Constructora</t>
-  </si>
-  <si>
-    <t>+502 4788-8041</t>
-  </si>
-  <si>
-    <t>La Torre</t>
-  </si>
-  <si>
-    <t>Alto</t>
-  </si>
-  <si>
-    <t>Supermercado</t>
-  </si>
-  <si>
-    <t>+502 4793-1527</t>
-  </si>
-  <si>
-    <t>El Progreso</t>
-  </si>
-  <si>
-    <t>Contructora</t>
-  </si>
-  <si>
-    <t>+502 2338-9100</t>
-  </si>
-  <si>
-    <t>Estudio G Diseño</t>
+    <t>Estudio G</t>
   </si>
   <si>
     <t>Intermedio</t>
@@ -447,7 +414,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -480,64 +447,13 @@
         <v>6</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3">
-        <v>75</v>
-      </c>
-      <c r="D3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4">
-        <v>100</v>
-      </c>
-      <c r="D4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5">
-        <v>6</v>
-      </c>
-      <c r="D5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" t="s">
-        <v>19</v>
       </c>
     </row>
   </sheetData>
